--- a/AAAGameData/DataTables/Item/ItemWithEffectTable_Equipment.xlsx
+++ b/AAAGameData/DataTables/Item/ItemWithEffectTable_Equipment.xlsx
@@ -62,10 +62,10 @@
     <t>SpriteName</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
+    <t>NameKey</t>
+  </si>
+  <si>
+    <t>DescriptionKey</t>
   </si>
   <si>
     <t>Tags</t>

--- a/AAAGameData/DataTables/Item/ItemWithEffectTable_Equipment.xlsx
+++ b/AAAGameData/DataTables/Item/ItemWithEffectTable_Equipment.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="132">
   <si>
     <t>#</t>
   </si>
@@ -144,124 +144,304 @@
     <t>物品类型标签</t>
   </si>
   <si>
-    <t>Equipment_Aaa</t>
+    <t>Equipment_DullAxe</t>
   </si>
   <si>
     <t>ItemRarity.Common</t>
   </si>
   <si>
-    <t>[PhysicalAtk,3]</t>
-  </si>
-  <si>
-    <t>3,5</t>
-  </si>
-  <si>
-    <t>攻击时有&lt;num1&gt;概率造成&lt;num2&gt;秒击晕</t>
-  </si>
-  <si>
-    <t>UI/IconMisc/Icon_Star_On.png</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Name.Aaa</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Description.Aaa</t>
-  </si>
-  <si>
-    <t>ItemTag.AAA</t>
-  </si>
-  <si>
-    <t>Equipment_Bbb</t>
+    <t>[PhysicalAtk,3],[SpecialAtk,-2]</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip4_41.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.DullAxe</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.DullAxe</t>
+  </si>
+  <si>
+    <t>ItemTag.Starting,ItemTag.Relic</t>
+  </si>
+  <si>
+    <t>Equipment_GreenCrystal</t>
+  </si>
+  <si>
+    <t>[MaxHP,5]</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip5_18.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.GreenCrystal</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.GreenCrystal</t>
+  </si>
+  <si>
+    <t>ItemTag.Relic</t>
+  </si>
+  <si>
+    <t>Equipment_HeavyBlade</t>
+  </si>
+  <si>
+    <t>物攻+&lt;percent1&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip1_6.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.HeavyBlade</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.HeavyBlade</t>
+  </si>
+  <si>
+    <t>Equipment_PsychicPearl</t>
+  </si>
+  <si>
+    <t>弹道数量+&lt;num1&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip4_42.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.PsychicPearl</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.PsychicPearl</t>
+  </si>
+  <si>
+    <t>Equipment_CursedTwinScythes</t>
+  </si>
+  <si>
+    <t>0.75,0.75,-0.75</t>
+  </si>
+  <si>
+    <t>物攻+&lt;percent1&gt;，特攻+&lt;percent2&gt;，生命上限+&lt;percent3&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip4_45.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.CursedTwinScythes</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.CursedTwinScythes</t>
+  </si>
+  <si>
+    <t>Equipment_WisdomStaff</t>
+  </si>
+  <si>
+    <t>0.1,0.15</t>
+  </si>
+  <si>
+    <t>特攻+&lt;percent1&gt;，特防+&lt;percent2&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip5_10.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.WisdomStaff</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.WisdomStaff</t>
+  </si>
+  <si>
+    <t>Equipment_TightHelmet</t>
+  </si>
+  <si>
+    <t>0.3,-0.2</t>
+  </si>
+  <si>
+    <t>物防+&lt;percent1&gt;，物攻+&lt;percent2&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip2_0.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.TightHelmet</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.TightHelmet</t>
+  </si>
+  <si>
+    <t>Equipment_HarvestGem</t>
+  </si>
+  <si>
+    <t>所有资源采集量+&lt;percent1&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip4-10.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.HarvestGem</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.HarvestGem</t>
+  </si>
+  <si>
+    <t>Equipment_HeavyPickaxe</t>
+  </si>
+  <si>
+    <t>0.5,-0.25</t>
+  </si>
+  <si>
+    <t>矿石类采集量+&lt;percent1&gt;，木材类采集量+&lt;percent2&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip4_33.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.HeavyPickaxe</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.HeavyPickaxe</t>
+  </si>
+  <si>
+    <t>Equipment_FocusAmber</t>
+  </si>
+  <si>
+    <t>0.25,-0.15</t>
+  </si>
+  <si>
+    <t>经验获取量+&lt;percent1&gt;，但采集量+&lt;percent2&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip2_37.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.FocusAmber</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.FocusAmber</t>
+  </si>
+  <si>
+    <t>Equipment_MysteriousJade</t>
+  </si>
+  <si>
+    <t>所有技能初始等级+&lt;num1&gt;</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip2_43.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.MysteriousJade</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.MysteriousJade</t>
+  </si>
+  <si>
+    <t>Equipment_SmartKey</t>
+  </si>
+  <si>
+    <t>可以撬开+&lt;num1&gt;级的锁</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip4_21.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.SmartKey</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.SmartKey</t>
+  </si>
+  <si>
+    <t>Equipment_PatchShoes</t>
   </si>
   <si>
     <t>ItemRarity.Rare</t>
   </si>
   <si>
-    <t>[PhysicalAtk,2],[PhysicalDef,2]</t>
-  </si>
-  <si>
-    <t>攻击时回复&lt;num1&gt;生命</t>
-  </si>
-  <si>
-    <t>UI/IconMisc/Icon_Star_Off.png</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Name.Bbb</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Description.Bbb</t>
-  </si>
-  <si>
-    <t>ItemTag.BBB,ItemTag.AAA</t>
-  </si>
-  <si>
-    <t>Equipment_Ccc</t>
+    <t>[stamina,40],[MoveSpeed,-60]</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip5_44.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.PatchShoes</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.PatchShoes</t>
+  </si>
+  <si>
+    <t>Equipment_SlaughterMask</t>
+  </si>
+  <si>
+    <t>击杀敌人时恢复&lt;percent1&gt;最大生命值</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip2_2.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.SlaughterMask</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.SlaughterMask</t>
+  </si>
+  <si>
+    <t>Equipment_RoundShield</t>
+  </si>
+  <si>
+    <t>+&lt;percent1&gt;正面减伤</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip5_25.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.RoundShield</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.RoundShield</t>
+  </si>
+  <si>
+    <t>Equipment_LevitationClothes</t>
+  </si>
+  <si>
+    <t>+&lt;percent1&gt;岩系减伤</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip5_16.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.LevitationClothes</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.LevitationClothes</t>
+  </si>
+  <si>
+    <t>Equipment_RippleArmband</t>
+  </si>
+  <si>
+    <t>+&lt;percent1&gt;水系伤害</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip1_15.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.RippleArmband</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.RippleArmband</t>
+  </si>
+  <si>
+    <t>Equipment_ThunderHeadpiece</t>
   </si>
   <si>
     <t>ItemRarity.Epic</t>
   </si>
   <si>
-    <t>[SpecialAtk,3]</t>
-  </si>
-  <si>
-    <t>0.6,3</t>
-  </si>
-  <si>
-    <t>攻击时回复&lt;num1&gt;生命和&lt;num2&gt;魔法</t>
-  </si>
-  <si>
-    <t>UI/IconMisc/Icon_Setting.png</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Name.Ccc</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Description.Ccc</t>
-  </si>
-  <si>
-    <t>Equipment_Ddd</t>
-  </si>
-  <si>
-    <t>ItemRarity.Legendary</t>
-  </si>
-  <si>
-    <t>[SpecialAtk,5],[PhysicalAtk,-3]</t>
-  </si>
-  <si>
-    <t>4,0.5,200</t>
-  </si>
-  <si>
-    <t>&lt;num1&gt;&lt;num2&gt;&lt;num3&gt;</t>
-  </si>
-  <si>
-    <t>UI/IconMisc/Icon_Close02.png</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Name.Ddd</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Description.Ddd</t>
-  </si>
-  <si>
-    <t>Equipment_Eee</t>
-  </si>
-  <si>
-    <t>ItemRarity.Heroic</t>
-  </si>
-  <si>
-    <t>[PhysicalDef,2],[SpecialDef,2]</t>
-  </si>
-  <si>
-    <t>&lt;num1&gt;</t>
-  </si>
-  <si>
-    <t>UI/IconMisc/Icon_Check03_s.png</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Name.Eee</t>
-  </si>
-  <si>
-    <t>Item.Equipment.Description.Eee</t>
+    <t>使用电系伤害击杀敌人时叠加1层过荷效果，每层过荷+&lt;percent1&gt;电系伤害</t>
+  </si>
+  <si>
+    <t>UI/IconEquip/equip1_47.png</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.ThunderHeadpiece</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.ThunderHeadpiece</t>
   </si>
 </sst>
 </file>
@@ -890,11 +1070,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1214,7 +1396,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1233,7 +1415,7 @@
     <col min="14" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1361,7 +1543,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" ht="42.75" spans="2:13">
+    <row r="5" ht="28.75" spans="1:13">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1377,163 +1559,555 @@
       <c r="G5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="6" ht="28.75" spans="2:13">
+    <row r="6" ht="28.75" spans="1:13">
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="1">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>48</v>
-      </c>
     </row>
-    <row r="7" ht="28.75" spans="2:13">
+    <row r="7" ht="28.75" spans="1:13">
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="1">
-        <v>5</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="8" ht="28.75" spans="2:13">
+    <row r="8" ht="28.75" spans="1:13">
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="9" ht="28.75" spans="2:13">
+    <row r="9" ht="56.75" spans="1:13">
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="28.75" spans="1:13">
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="M10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" ht="28.75" spans="1:13">
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="1">
-        <v>15.6</v>
-      </c>
-      <c r="I9" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>40</v>
+      <c r="L11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" ht="28.75" spans="1:13">
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="28.75" spans="1:13">
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="28.75" spans="1:13">
+      <c r="B14" s="1">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="28.75" spans="1:13">
+      <c r="B15" s="1">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" ht="28.75" spans="1:13">
+      <c r="B16" s="1">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" ht="28.75" spans="2:13">
+      <c r="B17" s="1">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" ht="42.75" spans="2:13">
+      <c r="B18" s="1">
+        <v>14</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" ht="28.75" spans="2:13">
+      <c r="B19" s="1">
+        <v>15</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" ht="28.75" spans="2:13">
+      <c r="B20" s="1">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" ht="28.75" spans="2:13">
+      <c r="B21" s="1">
+        <v>17</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" ht="28.75" spans="2:13">
+      <c r="B22" s="1">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
